--- a/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E43E6B1D-6B8C-4B84-9460-796291C14E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1346E80D-32CE-4280-B9A6-34EA29A60D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{571DA51D-4F7A-41C3-93E5-22B82B56CD5A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6DCD8F1A-34CC-45DF-A04D-851278E7869D}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3418,7 +3418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8674CC91-CC62-4531-80F0-6377C4515FEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D67F6F-A101-4A81-886D-706CE99AD3E7}">
   <dimension ref="B3:L417"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
